--- a/Cplusplus/02. C++ FOUNDATIONS.xlsx
+++ b/Cplusplus/02. C++ FOUNDATIONS.xlsx
@@ -14,6 +14,7 @@
   <sheets>
     <sheet name="CheckList C++" sheetId="1" r:id="rId1"/>
     <sheet name="C++ FOUNDATIONS" sheetId="2" r:id="rId2"/>
+    <sheet name="Questions" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="571">
   <si>
     <t>1. Basic Syntax &amp; Data Types</t>
   </si>
@@ -584,18 +585,12 @@
     <t xml:space="preserve">    n *= 2;  // Nhân đôi mỗi phần tử</t>
   </si>
   <si>
-    <t>// auto: Tự suy kiểu</t>
-  </si>
-  <si>
     <t>for (auto&amp; item : nums) {</t>
   </si>
   <si>
     <t xml:space="preserve">    item += 10;</t>
   </si>
   <si>
-    <t>// const auto&amp;: Đọc hiệu quả (không copy)</t>
-  </si>
-  <si>
     <t>for (const auto&amp; str : stringVector) {</t>
   </si>
   <si>
@@ -1536,87 +1531,6 @@
   </si>
   <si>
     <t>string weird = R"abc(He said: "Raw (string)")abc";</t>
-  </si>
-  <si>
-    <t>CÁC BẪY PHỔ BIẾN &amp; BEST PRACTICES</t>
-  </si>
-  <si>
-    <t>1. Memory Leaks</t>
-  </si>
-  <si>
-    <t>// SAI</t>
-  </si>
-  <si>
-    <t>int* ptr = new int[100];</t>
-  </si>
-  <si>
-    <t>// Quên delete[] → memory leak</t>
-  </si>
-  <si>
-    <t>// ĐÚNG</t>
-  </si>
-  <si>
-    <t>delete[] ptr;</t>
-  </si>
-  <si>
-    <t>// Hoặc dùng smart pointers/vector</t>
-  </si>
-  <si>
-    <t>2. Uninitialized Variables</t>
-  </si>
-  <si>
-    <t>int x;           // Garbage value</t>
-  </si>
-  <si>
-    <t>cout &lt;&lt; x;       // Undefined behavior</t>
-  </si>
-  <si>
-    <t>int y = 0;       // Luôn khởi tạo!</t>
-  </si>
-  <si>
-    <t>3. Off-by-One Errors</t>
-  </si>
-  <si>
-    <t>int arr[5];</t>
-  </si>
-  <si>
-    <t>for (int i = 0; i &lt;= 5; i++) {  // SAI! Nên i &lt; 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    arr[i] = 0;  // arr[5] out of bounds</t>
-  </si>
-  <si>
-    <t>4. Integer Overflow</t>
-  </si>
-  <si>
-    <t>int big = 2147483647;</t>
-  </si>
-  <si>
-    <t>big++;  // Overflow thành -2147483648</t>
-  </si>
-  <si>
-    <t>5. Comparing Floats</t>
-  </si>
-  <si>
-    <t>if (0.1 + 0.2 == 0.3) { }  // False do rounding error</t>
-  </si>
-  <si>
-    <t>if (abs((0.1 + 0.2) - 0.3) &lt; 0.00001) { }</t>
-  </si>
-  <si>
-    <t>ỨNG DỤNG PHỔ BIẾN</t>
-  </si>
-  <si>
-    <t>Tóm tắt các điểm quan trọng:</t>
-  </si>
-  <si>
-    <t>Luôn khởi tạo biến, kiểm tra bounds</t>
-  </si>
-  <si>
-    <t>Modern C++ (C++11+): range-based for, auto, lambda</t>
-  </si>
-  <si>
-    <t>Tránh raw pointers khi có thể, dùng smart pointers</t>
   </si>
   <si>
     <r>
@@ -1844,79 +1758,6 @@
   </si>
   <si>
     <r>
-      <t>Lời khuyên:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Dùng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>const</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>constexpr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> thay vì </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>#define</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> khi có thể!</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>for</t>
     </r>
     <r>
@@ -2000,225 +1841,6 @@
   </si>
   <si>
     <r>
-      <t>1. Game Development</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Control flow, arrays cho game states</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2. System Programming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Pointers, memory management</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3. Algorithm Contests</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Fast I/O, array manipulation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>4. Embedded Systems</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Efficient loops, bit operations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>5. Desktop Applications</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: String processing, data structures</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>6. Scientific Computing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Arrays, precision types (double)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>7. Web Backends</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: String parsing, JSON handling</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ưu tiên </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>std::string</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>std::vector</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> thay vì C-style</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dùng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>const</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>constexpr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> thay vì </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>#define</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Truyền object lớn bằng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>const reference</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Cảnh báo</t>
     </r>
     <r>
@@ -2236,12 +1858,478 @@
   <si>
     <t>// dynamic_cast: Chuyển đổi trong inheritance (kế thừa), kiểm tra runtime</t>
   </si>
+  <si>
+    <t>1. Con trỏ void có thể trỏ đến mọi loại giá trị?</t>
+  </si>
+  <si>
+    <t>int x = 10;</t>
+  </si>
+  <si>
+    <t>float y = 3.14;</t>
+  </si>
+  <si>
+    <t>void* ptr;</t>
+  </si>
+  <si>
+    <t>ptr = &amp;x;  // OK</t>
+  </si>
+  <si>
+    <t>ptr = &amp;y;  // OK</t>
+  </si>
+  <si>
+    <t>// int val = *ptr;  // LỖI! Không thể dereference void*</t>
+  </si>
+  <si>
+    <t>int val = *(int*)ptr;  // Đúng - phải ép kiểu trước</t>
+  </si>
+  <si>
+    <t>2. Tại sao con trỏ kiểu gì thường trỏ đến biến kiểu đó?</t>
+  </si>
+  <si>
+    <t>Lý do chính:</t>
+  </si>
+  <si>
+    <t>a) Kích thước vùng nhớ đọc/ghi</t>
+  </si>
+  <si>
+    <t>int x = 0x12345678;</t>
+  </si>
+  <si>
+    <t>int* p_int = &amp;x;</t>
+  </si>
+  <si>
+    <t>char* p_char = (char*)&amp;x;</t>
+  </si>
+  <si>
+    <t>printf("%x\n", *p_int);    // Đọc 4 bytes: 12345678</t>
+  </si>
+  <si>
+    <t>printf("%x\n", *p_char);   // Đọc 1 byte:  78 (hoặc 12 tùy endianness)</t>
+  </si>
+  <si>
+    <t>b) Pointer Arithmetic (Số học con trỏ)</t>
+  </si>
+  <si>
+    <t>Kiểu con trỏ quyết định khoảng cách khi tăng/giảm:</t>
+  </si>
+  <si>
+    <t>int arr[] = {10, 20, 30};</t>
+  </si>
+  <si>
+    <t>int* p = arr;</t>
+  </si>
+  <si>
+    <t>char* q = (char*)arr;</t>
+  </si>
+  <si>
+    <t>p++;  // Tăng 4 bytes (sizeof(int))</t>
+  </si>
+  <si>
+    <t>q++;  // Tăng 1 byte (sizeof(char))</t>
+  </si>
+  <si>
+    <t>c) An toàn kiểu (Type Safety)</t>
+  </si>
+  <si>
+    <t>Giúp compiler phát hiện lỗi:</t>
+  </si>
+  <si>
+    <t>float* p = &amp;x;  // Warning! Kiểu không khớp</t>
+  </si>
+  <si>
+    <t>3. Con trỏ cha trỏ đến đối tượng con trong lập trình nhúng?</t>
+  </si>
+  <si>
+    <t>class Sensor {  // Base class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    virtual void read() = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    virtual ~Sensor() {}</t>
+  </si>
+  <si>
+    <t>class TemperatureSensor : public Sensor {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void read() override { /* đọc nhiệt độ */ }</t>
+  </si>
+  <si>
+    <t>class PressureSensor : public Sensor {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void read() override { /* đọc áp suất */ }</t>
+  </si>
+  <si>
+    <t>// Observer pattern trong nhúng</t>
+  </si>
+  <si>
+    <t>Sensor* sensors[10];  // Mảng con trỏ base class</t>
+  </si>
+  <si>
+    <t>sensors[0] = new TemperatureSensor();</t>
+  </si>
+  <si>
+    <t>sensors[1] = new PressureSensor();</t>
+  </si>
+  <si>
+    <t>// Polling tất cả sensors</t>
+  </si>
+  <si>
+    <t>for(int i = 0; i &lt; 10; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if(sensors[i]) sensors[i]-&gt;read();  // Polymorphic call</t>
+  </si>
+  <si>
+    <t>Lợi ích trong embedded:</t>
+  </si>
+  <si>
+    <t>Quản lý nhiều loại sensor/actuator đồng nhất</t>
+  </si>
+  <si>
+    <t>Dễ mở rộng thêm thiết bị mới</t>
+  </si>
+  <si>
+    <t>Code gọn, dễ bảo trì</t>
+  </si>
+  <si>
+    <t>4. Ép kiểu trong C++ - Upcasting vs Downcasting?</t>
+  </si>
+  <si>
+    <t>Upcasting (Con → Cha): AN TOÀN</t>
+  </si>
+  <si>
+    <t>class Animal { virtual void sound() {} };</t>
+  </si>
+  <si>
+    <t>class Dog : public Animal { void sound() override { bark(); } };</t>
+  </si>
+  <si>
+    <t>Dog* dog = new Dog();</t>
+  </si>
+  <si>
+    <t>Animal* animal = dog;  // Upcast - Luôn an toàn, tự động</t>
+  </si>
+  <si>
+    <t>Không cần ép kiểu tường minh</t>
+  </si>
+  <si>
+    <t>Luôn hợp lệ vì "mọi con chó đều là động vật"</t>
+  </si>
+  <si>
+    <t>Downcasting (Cha → Con): NGUY HIỂM</t>
+  </si>
+  <si>
+    <t>Animal* animal = new Animal();</t>
+  </si>
+  <si>
+    <t>Dog* dog = (Dog*)animal;  // C-style cast - NGUY HIỂM!</t>
+  </si>
+  <si>
+    <t>dog-&gt;bark();  // UB! animal không thực sự là Dog</t>
+  </si>
+  <si>
+    <t>Vì sao nguy hiểm?</t>
+  </si>
+  <si>
+    <t>Con trỏ cha có thể trỏ đến đối tượng không phải con</t>
+  </si>
+  <si>
+    <t>Truy xuất thành viên không tồn tại → Undefined Behavior</t>
+  </si>
+  <si>
+    <t>Animal* animal = getAnimal();  // Không biết là gì</t>
+  </si>
+  <si>
+    <t>Dog* dog = dynamic_cast&lt;Dog*&gt;(animal);</t>
+  </si>
+  <si>
+    <t>if(dog) {  // Kiểm tra thành công</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    dog-&gt;bark();  // An toàn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // animal không phải Dog</t>
+  </si>
+  <si>
+    <t>Có runtime overhead nhẹ</t>
+  </si>
+  <si>
+    <r>
+      <t>Đúng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, nhưng cần hiểu rõ hơn:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Phải </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ép kiểu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> về đúng kiểu dữ liệu trước khi sử dụng</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Đúng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, đây là pattern rất phổ biến - gọi là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Polymorphism</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Con trỏ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>void* có thể lưu địa chỉ của bất kỳ kiểu dữ liệu nào</t>
+    </r>
+  </si>
+  <si>
+    <t>Giải pháp: dynamic_cast</t>
+  </si>
+  <si>
+    <t>dynamic_cast yêu cầu:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Class phải có ít nhất 1 hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>virtual (có RTTI)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trả về </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nullptr nếu ép kiểu thất bại</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tuy nhiên, bạn </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không thể truy xuất giá trị</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trực tiếp qua void*</t>
+    </r>
+  </si>
+  <si>
+    <t>Kiểu con trỏ quyết định bao nhiêu byte được đọc khi dereference:</t>
+  </si>
+  <si>
+    <r>
+      <t>Lời khuyên:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>const</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>constexpr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thay vì </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#define</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> khi có thể!</t>
+    </r>
+  </si>
+  <si>
+    <t>// const auto&amp;: Đọc hiệu quả (chắc chắn không copy) - compiler thấy tốt nhất</t>
+  </si>
+  <si>
+    <t>// auto: Tự suy kiểu : Đọc hiệu quả (không copy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // ...</t>
+  </si>
+  <si>
+    <t>Cú pháp</t>
+  </si>
+  <si>
+    <t>Trình biên dịch sẽ “dịch” ra tương đương như sau:</t>
+  </si>
+  <si>
+    <t>for (auto it = container.begin(); it != container.end(); ++it) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    auto element = *it;   // &lt;-- đây là điểm quan trọng!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for (declaration : container) { </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // container = vector, queue, deque, … bất kỳ loại nào có .begine, .end)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2305,6 +2393,20 @@
       <color rgb="FFFF0000"/>
       <name val="Arial Unicode MS"/>
       <charset val="163"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="6">
@@ -2375,7 +2477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2424,6 +2526,26 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2927,18 +3049,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V735"/>
+  <dimension ref="A1:AJ597"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="16384" width="3" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="16" customFormat="1" ht="15.75" thickBot="1">
+    <row r="1" spans="1:36" s="16" customFormat="1" ht="15.75" thickBot="1">
       <c r="A1" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15">
+    <row r="2" spans="1:36" ht="15">
       <c r="A2" s="17" t="s">
         <v>43</v>
       </c>
@@ -2947,8 +3069,18 @@
       <c r="D2" s="18"/>
       <c r="E2" s="18"/>
       <c r="F2" s="18"/>
-    </row>
-    <row r="3" spans="1:9" ht="15">
+      <c r="AC2" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD2" s="18"/>
+      <c r="AE2" s="18"/>
+      <c r="AF2" s="18"/>
+      <c r="AG2" s="18"/>
+      <c r="AH2" s="18"/>
+      <c r="AI2" s="18"/>
+      <c r="AJ2" s="18"/>
+    </row>
+    <row r="3" spans="1:36" ht="15">
       <c r="A3" s="20" t="s">
         <v>44</v>
       </c>
@@ -2960,68 +3092,118 @@
       <c r="G3" s="21"/>
       <c r="H3" s="21"/>
       <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="AC3" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21"/>
+      <c r="AF3" s="21"/>
+      <c r="AG3" s="21"/>
+      <c r="AH3" s="21"/>
+    </row>
+    <row r="4" spans="1:36">
       <c r="B4" s="8" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="AC4" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36">
       <c r="B5" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="AC5" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36">
       <c r="B6" s="8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="AC6" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36">
       <c r="B7" s="8" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="AC7" s="9"/>
+    </row>
+    <row r="8" spans="1:36">
       <c r="B8" s="8" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="AC8" s="12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36">
       <c r="B9" s="8" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="15">
+      <c r="AC9" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36">
+      <c r="AC10" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" ht="15">
       <c r="A11" s="11" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="AC11" s="9"/>
+    </row>
+    <row r="12" spans="1:36">
       <c r="B12" s="8" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>466</v>
+      </c>
+      <c r="AC12" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36">
       <c r="B13" s="8" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>467</v>
+      </c>
+      <c r="AC13" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36">
       <c r="B14" s="8" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>468</v>
+      </c>
+      <c r="AC14" s="12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" ht="15">
       <c r="B15" s="8" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>469</v>
+      </c>
+      <c r="AC15" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36">
       <c r="B16" s="8" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="15">
+        <v>470</v>
+      </c>
+      <c r="AC16" s="8" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34">
+      <c r="AC17" s="8" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" ht="15">
       <c r="A18" s="20" t="s">
         <v>52</v>
       </c>
@@ -3031,20 +3213,34 @@
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:34" ht="15">
       <c r="B19" s="8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="AC19" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD19" s="21"/>
+      <c r="AE19" s="21"/>
+      <c r="AF19" s="21"/>
+      <c r="AG19" s="21"/>
+      <c r="AH19" s="21"/>
+    </row>
+    <row r="20" spans="1:34">
       <c r="B20" s="8" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="AC20" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34">
       <c r="B21" s="9"/>
-    </row>
-    <row r="22" spans="1:18">
+      <c r="AC21" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34">
       <c r="B22" s="12" t="s">
         <v>55</v>
       </c>
@@ -3064,8 +3260,11 @@
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="AC22" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34">
       <c r="B23" s="12" t="s">
         <v>56</v>
       </c>
@@ -3085,8 +3284,9 @@
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
-    </row>
-    <row r="24" spans="1:18">
+      <c r="AC23" s="9"/>
+    </row>
+    <row r="24" spans="1:34">
       <c r="B24" s="12" t="s">
         <v>57</v>
       </c>
@@ -3106,99 +3306,157 @@
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
-    </row>
-    <row r="26" spans="1:18" ht="15">
+      <c r="AC24" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34">
+      <c r="AC25" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34" ht="15">
       <c r="A26" s="11" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="27" spans="1:18">
+      <c r="AC26" s="9"/>
+    </row>
+    <row r="27" spans="1:34">
       <c r="B27" s="9" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
+        <v>471</v>
+      </c>
+      <c r="AC27" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:34">
       <c r="B28" s="9" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="15">
+        <v>472</v>
+      </c>
+      <c r="AC28" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" ht="15">
       <c r="A29" s="14" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
+        <v>483</v>
+      </c>
+      <c r="AC29" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34">
       <c r="B30" s="8" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="31" spans="1:18">
+      <c r="AC30" s="9"/>
+    </row>
+    <row r="31" spans="1:34">
       <c r="B31" s="8" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="32" spans="1:18">
+      <c r="AC31" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34">
       <c r="B32" s="8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="AC32" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33">
       <c r="B33" s="8" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="34" spans="1:22">
+      <c r="AC33" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" ht="15">
       <c r="B34" s="8" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="36" spans="1:22" ht="15">
+      <c r="AC34" s="29" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" ht="15">
       <c r="A36" s="20" t="s">
         <v>64</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
       <c r="D36" s="21"/>
-    </row>
-    <row r="37" spans="1:22" ht="15">
+      <c r="AC36" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="AD36" s="21"/>
+      <c r="AE36" s="21"/>
+      <c r="AF36" s="21"/>
+      <c r="AG36" s="21"/>
+    </row>
+    <row r="37" spans="1:33" ht="15">
       <c r="B37" s="19" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="38" spans="1:22">
+      <c r="AC37" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33">
       <c r="B38" s="8" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="39" spans="1:22">
+      <c r="AC38" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33">
       <c r="B39" s="8" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="40" spans="1:22">
+      <c r="AC39" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33">
       <c r="A40" s="9"/>
-    </row>
-    <row r="41" spans="1:22" ht="15">
+      <c r="AC40" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" ht="15">
       <c r="B41" s="19" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22">
+        <v>484</v>
+      </c>
+      <c r="AC41" s="9"/>
+    </row>
+    <row r="42" spans="1:33">
       <c r="B42" s="8" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="43" spans="1:22">
+      <c r="AC42" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33">
       <c r="B43" s="8" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="44" spans="1:22">
+      <c r="AC43" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33">
       <c r="B44" s="8" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="45" spans="1:22">
+      <c r="AC44" s="9"/>
+    </row>
+    <row r="45" spans="1:33">
       <c r="B45" s="12" t="s">
         <v>71</v>
       </c>
@@ -3222,1019 +3480,1376 @@
       <c r="T45" s="13"/>
       <c r="U45" s="13"/>
       <c r="V45" s="13"/>
-    </row>
-    <row r="46" spans="1:22">
+      <c r="AC45" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33">
       <c r="A46" s="9"/>
-    </row>
-    <row r="47" spans="1:22" ht="15">
+      <c r="AC46" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" ht="15">
       <c r="B47" s="19" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="48" spans="1:22">
+      <c r="AC47" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33">
       <c r="B48" s="8" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="49" spans="1:2">
+      <c r="AC48" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29">
       <c r="B49" s="8" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="50" spans="1:2">
+      <c r="AC49" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29">
       <c r="B50" s="9"/>
     </row>
-    <row r="51" spans="1:2" ht="15">
+    <row r="51" spans="1:29" ht="15">
       <c r="B51" s="19" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:29">
       <c r="B52" s="8" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:29">
       <c r="B53" s="8" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15">
+    <row r="55" spans="1:29" ht="15">
       <c r="A55" s="11" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:29">
       <c r="A56" s="9"/>
       <c r="B56" s="8" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29">
       <c r="B57" s="8" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="58" spans="1:29">
       <c r="B58" s="8" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="59" spans="1:29">
       <c r="B59" s="8" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="15">
-      <c r="A62" s="7" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="61" spans="1:29" ht="15">
+      <c r="A61" s="20" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="63" spans="1:2">
+      <c r="B61" s="21"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+    </row>
+    <row r="62" spans="1:29">
+      <c r="B62" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29">
       <c r="B63" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:29">
       <c r="B64" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="B65" s="8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
-      <c r="B66" s="9"/>
-    </row>
-    <row r="67" spans="1:2">
+    <row r="65" spans="1:34">
+      <c r="B65" s="9"/>
+    </row>
+    <row r="66" spans="1:34">
+      <c r="B66" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="1:34">
       <c r="B67" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" spans="1:34">
       <c r="B68" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="B69" s="8" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
-      <c r="B70" s="9"/>
-    </row>
-    <row r="71" spans="1:2">
+    <row r="69" spans="1:34">
+      <c r="B69" s="9"/>
+    </row>
+    <row r="70" spans="1:34">
+      <c r="B70" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="71" spans="1:34">
       <c r="B71" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:34">
       <c r="B72" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="B73" s="8" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15">
-      <c r="A78" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" ht="15">
-      <c r="A80" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
+    <row r="73" spans="1:34" ht="15" thickBot="1"/>
+    <row r="74" spans="1:34" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A74" s="15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="75" spans="1:34" ht="15">
+      <c r="A75" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="AC75" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="AD75" s="18"/>
+      <c r="AE75" s="18"/>
+      <c r="AF75" s="18"/>
+      <c r="AG75" s="18"/>
+    </row>
+    <row r="76" spans="1:34" ht="15">
+      <c r="A76" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B76" s="21"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="21"/>
+      <c r="AC76" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="AD76" s="21"/>
+      <c r="AE76" s="21"/>
+      <c r="AF76" s="21"/>
+      <c r="AG76" s="21"/>
+      <c r="AH76" s="21"/>
+    </row>
+    <row r="77" spans="1:34">
+      <c r="A77" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC77" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="78" spans="1:34">
+      <c r="A78" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC78" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="79" spans="1:34">
+      <c r="A79" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC79" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="80" spans="1:34">
+      <c r="A80" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC80" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29">
+      <c r="A81" s="9"/>
+      <c r="AC81" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="82" spans="1:29">
       <c r="A82" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
+        <v>131</v>
+      </c>
+      <c r="AC82" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29">
       <c r="A83" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
+        <v>132</v>
+      </c>
+      <c r="AC83" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29">
       <c r="A84" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="9"/>
-    </row>
-    <row r="86" spans="1:1">
+        <v>133</v>
+      </c>
+      <c r="AC84" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="85" spans="1:29">
+      <c r="A85" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="AC85" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="86" spans="1:29">
       <c r="A86" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
+        <v>130</v>
+      </c>
+      <c r="AC86" s="9"/>
+    </row>
+    <row r="87" spans="1:29">
+      <c r="A87" s="9"/>
+      <c r="AC87" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="88" spans="1:29">
       <c r="A88" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="9"/>
-    </row>
-    <row r="90" spans="1:1">
+        <v>135</v>
+      </c>
+      <c r="AC88" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="89" spans="1:29">
+      <c r="A89" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC89" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="90" spans="1:29">
       <c r="A90" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
+        <v>137</v>
+      </c>
+      <c r="AC90" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29">
       <c r="A91" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
+        <v>138</v>
+      </c>
+      <c r="AC91" s="8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="92" spans="1:29">
       <c r="A92" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" ht="15">
-      <c r="A94" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="9"/>
-    </row>
-    <row r="96" spans="1:1">
+        <v>139</v>
+      </c>
+      <c r="AC92" s="8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="93" spans="1:29">
+      <c r="A93" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC93" s="8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="94" spans="1:29">
+      <c r="AC94" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="95" spans="1:29" ht="15">
+      <c r="A95" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC95" s="8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="96" spans="1:29">
       <c r="A96" s="8" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
+        <v>479</v>
+      </c>
+      <c r="AC96" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="97" spans="1:34">
       <c r="A97" s="8" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" ht="15">
-      <c r="A99" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
+        <v>480</v>
+      </c>
+      <c r="AC97" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="98" spans="1:34">
+      <c r="A98" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="AC98" s="8" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="99" spans="1:34">
+      <c r="AC99" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="100" spans="1:34" ht="15">
+      <c r="A100" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B100" s="13"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13"/>
+      <c r="G100" s="13"/>
+      <c r="H100" s="13"/>
+    </row>
+    <row r="101" spans="1:34" ht="15">
       <c r="A101" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="9"/>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
+        <v>565</v>
+      </c>
+      <c r="AC101" s="11" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="102" spans="1:34" ht="15">
+      <c r="A102" s="29" t="s">
+        <v>569</v>
+      </c>
+      <c r="AC102" s="8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="103" spans="1:34" ht="15">
+      <c r="A103" s="31" t="s">
+        <v>570</v>
+      </c>
+      <c r="AC103" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="104" spans="1:34" ht="15">
+      <c r="A104" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC104" s="8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="105" spans="1:34">
+      <c r="A105" t="s">
+        <v>566</v>
+      </c>
+      <c r="AC105" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="106" spans="1:34">
       <c r="A106" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="9"/>
-    </row>
-    <row r="108" spans="1:1">
+        <v>567</v>
+      </c>
+      <c r="AC106" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="107" spans="1:34">
+      <c r="A107" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="AC107" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="108" spans="1:34">
       <c r="A108" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
+        <v>564</v>
+      </c>
+      <c r="AC108" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="109" spans="1:34">
       <c r="A109" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="9"/>
-    </row>
-    <row r="112" spans="1:1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="110" spans="1:34" ht="15">
+      <c r="A110" s="8"/>
+      <c r="AC110" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="AD110" s="21"/>
+      <c r="AE110" s="21"/>
+      <c r="AF110" s="21"/>
+      <c r="AG110" s="21"/>
+      <c r="AH110" s="21"/>
+    </row>
+    <row r="111" spans="1:34">
+      <c r="A111" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC111" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="112" spans="1:34">
       <c r="A112" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
+        <v>144</v>
+      </c>
+      <c r="AC112" s="8" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="113" spans="1:36">
+      <c r="A113" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC113" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="114" spans="1:36">
       <c r="A114" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" ht="15">
-      <c r="A116" s="11" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" ht="15">
-      <c r="A118" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
+        <v>146</v>
+      </c>
+      <c r="AC114" s="9"/>
+    </row>
+    <row r="115" spans="1:36">
+      <c r="A115" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC115" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="116" spans="1:36">
+      <c r="A116" s="9"/>
+      <c r="AC116" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="117" spans="1:36">
+      <c r="A117" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="AC117" s="8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="118" spans="1:36">
+      <c r="A118" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC118" s="8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="119" spans="1:36">
+      <c r="A119" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AC119" s="8" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="120" spans="1:36">
       <c r="A120" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="9"/>
-    </row>
-    <row r="125" spans="1:1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="121" spans="1:36" ht="15">
+      <c r="A121" s="9"/>
+      <c r="AC121" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="AD121" s="21"/>
+      <c r="AE121" s="21"/>
+      <c r="AF121" s="21"/>
+      <c r="AG121" s="21"/>
+      <c r="AH121" s="21"/>
+      <c r="AI121" s="21"/>
+      <c r="AJ121" s="21"/>
+    </row>
+    <row r="122" spans="1:36">
+      <c r="A122" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="AC122" s="8" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="123" spans="1:36">
+      <c r="A123" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="AC123" s="8" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="124" spans="1:36">
+      <c r="A124" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="AC124" s="8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="125" spans="1:36">
       <c r="A125" s="8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="9"/>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" ht="15">
-      <c r="A136" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" ht="15">
-      <c r="A138" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" ht="15">
-      <c r="A140" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
+        <v>130</v>
+      </c>
+      <c r="AC125" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="126" spans="1:36">
+      <c r="A126" s="9"/>
+      <c r="AC126" s="9"/>
+    </row>
+    <row r="127" spans="1:36">
+      <c r="A127" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="B127" s="13"/>
+      <c r="AC127" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="128" spans="1:36">
+      <c r="A128" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B128" s="13"/>
+      <c r="AC128" s="8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="129" spans="1:29">
+      <c r="A129" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B129" s="13"/>
+      <c r="AC129" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="130" spans="1:29">
+      <c r="A130" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B130" s="13"/>
+      <c r="AC130" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="131" spans="1:29">
+      <c r="AC131" s="9"/>
+    </row>
+    <row r="132" spans="1:29" ht="15">
+      <c r="A132" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AC132" s="8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="133" spans="1:29">
+      <c r="A133" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="AC133" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="134" spans="1:29">
+      <c r="A134" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC134" s="8" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="135" spans="1:29">
+      <c r="A135" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC135" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="136" spans="1:29">
+      <c r="A136" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC136" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="137" spans="1:29">
+      <c r="A137" s="9"/>
+    </row>
+    <row r="138" spans="1:29">
+      <c r="A138" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="139" spans="1:29">
+      <c r="A139" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="140" spans="1:29">
+      <c r="A140" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="141" spans="1:29">
+      <c r="A141" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="143" spans="1:29" ht="15">
+      <c r="A143" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="B143" s="21"/>
+      <c r="C143" s="21"/>
+      <c r="D143" s="21"/>
+      <c r="E143" s="21"/>
+      <c r="F143" s="21"/>
+      <c r="G143" s="21"/>
+    </row>
+    <row r="144" spans="1:29">
       <c r="A144" s="8" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="9"/>
+      <c r="A146" s="8" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="8" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="8" t="s">
-        <v>133</v>
-      </c>
+      <c r="A149" s="9"/>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="8" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="9"/>
+      <c r="A152" s="8" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="8" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="8" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="8" t="s">
-        <v>137</v>
-      </c>
+      <c r="A155" s="9"/>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="8" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="8" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" ht="15">
-      <c r="A160" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="9"/>
-    </row>
-    <row r="162" spans="1:1">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
       <c r="A162" s="8" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" s="8" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" s="8" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" ht="15">
-      <c r="A166" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="15" thickBot="1"/>
+    <row r="164" spans="1:8" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A164" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="15">
+      <c r="A165" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="B165" s="18"/>
+      <c r="C165" s="18"/>
+      <c r="D165" s="18"/>
+      <c r="E165" s="18"/>
+      <c r="F165" s="18"/>
+    </row>
+    <row r="166" spans="1:8" ht="15">
+      <c r="A166" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="B166" s="21"/>
+      <c r="C166" s="21"/>
+      <c r="D166" s="21"/>
+      <c r="E166" s="21"/>
+      <c r="F166" s="21"/>
+      <c r="G166" s="21"/>
+      <c r="H166" s="21"/>
+    </row>
+    <row r="167" spans="1:8" ht="15">
+      <c r="A167" s="19" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
       <c r="A168" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
       <c r="A169" s="9"/>
     </row>
-    <row r="170" spans="1:1">
-      <c r="A170" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
+    <row r="170" spans="1:8" ht="15">
+      <c r="A170" s="19" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
       <c r="A171" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
       <c r="A172" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
       <c r="A173" s="8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="174" spans="1:1">
+    <row r="174" spans="1:8">
       <c r="A174" s="9"/>
     </row>
-    <row r="175" spans="1:1">
-      <c r="A175" s="8" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
+    <row r="175" spans="1:8" ht="15">
+      <c r="A175" s="19" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
       <c r="A176" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1">
-      <c r="A177" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="15">
+      <c r="A178" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B178" s="21"/>
+      <c r="C178" s="21"/>
+      <c r="D178" s="21"/>
+      <c r="E178" s="21"/>
+      <c r="F178" s="21"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" s="8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="179" spans="1:1">
-      <c r="A179" s="9"/>
-    </row>
-    <row r="180" spans="1:1">
-      <c r="A180" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1">
-      <c r="A182" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1">
-      <c r="A183" s="8" t="s">
+    <row r="183" spans="1:6">
+      <c r="A183" s="9"/>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" s="12" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" s="8" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" s="8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="184" spans="1:1">
-      <c r="A184" s="9"/>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1">
-      <c r="A186" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1">
-      <c r="A187" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1">
-      <c r="A188" s="8" t="s">
+    <row r="188" spans="1:6">
+      <c r="A188" s="9"/>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" s="12" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" s="8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="190" spans="1:1" ht="15">
-      <c r="A190" s="11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1">
-      <c r="A192" s="8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1">
-      <c r="A193" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
+    <row r="193" spans="1:2">
+      <c r="A193" s="9"/>
+    </row>
+    <row r="194" spans="1:2">
       <c r="A194" s="8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
       <c r="A195" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="9"/>
+    </row>
+    <row r="200" spans="1:2" ht="15">
+      <c r="A200" s="19" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="196" spans="1:1">
-      <c r="A196" s="9"/>
-    </row>
-    <row r="197" spans="1:1">
-      <c r="A197" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1">
-      <c r="A198" s="8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1">
-      <c r="A199" s="8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1">
-      <c r="A200" s="8" t="s">
+    <row r="205" spans="1:2" ht="15">
+      <c r="A205" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="B206" s="9" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" ht="15">
+      <c r="B207" s="14" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" ht="15">
+      <c r="B208" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="B209" s="9" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" ht="15">
+      <c r="A211" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="202" spans="1:1" ht="15">
-      <c r="A202" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1">
-      <c r="A204" s="8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1">
-      <c r="A205" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1">
-      <c r="A206" s="8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1">
-      <c r="A207" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1">
-      <c r="A208" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1">
-      <c r="A209" s="9"/>
-    </row>
-    <row r="210" spans="1:1">
-      <c r="A210" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1">
-      <c r="A211" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1">
-      <c r="A212" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1">
-      <c r="A213" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1">
-      <c r="A214" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1">
-      <c r="A215" s="9"/>
-    </row>
-    <row r="216" spans="1:1">
-      <c r="A216" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1">
+    <row r="216" spans="1:2">
+      <c r="A216" s="9"/>
+    </row>
+    <row r="217" spans="1:2">
       <c r="A217" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
       <c r="A218" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1">
-      <c r="A219" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="9"/>
+    </row>
+    <row r="220" spans="1:2">
       <c r="A220" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
       <c r="A221" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1">
-      <c r="A222" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1" ht="15">
-      <c r="A226" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1" ht="15">
-      <c r="A228" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" ht="15">
+      <c r="A223" s="7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="8" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="8" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="8" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="9"/>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="8" t="s">
-        <v>177</v>
+        <v>267</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" s="8" t="s">
-        <v>178</v>
+        <v>268</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="8" t="s">
-        <v>179</v>
+        <v>269</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="8" t="s">
-        <v>180</v>
+        <v>270</v>
       </c>
     </row>
     <row r="234" spans="1:1">
-      <c r="A234" s="8" t="s">
-        <v>181</v>
-      </c>
+      <c r="A234" s="9"/>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="8" t="s">
-        <v>182</v>
+        <v>271</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="8" t="s">
-        <v>183</v>
+        <v>272</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" s="8" t="s">
-        <v>184</v>
+        <v>273</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="8" t="s">
-        <v>130</v>
+        <v>274</v>
       </c>
     </row>
     <row r="239" spans="1:1">
-      <c r="A239" s="9"/>
+      <c r="A239" s="8" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1">
-      <c r="A241" s="8" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1">
-      <c r="A242" s="8" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1">
-      <c r="A243" s="8" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1">
-      <c r="A244" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1">
-      <c r="A245" s="8" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1">
-      <c r="A246" s="8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1">
-      <c r="A247" s="8" t="s">
-        <v>192</v>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" ht="15">
+      <c r="A244" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" ht="15">
+      <c r="A246" s="7" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" s="8" t="s">
-        <v>193</v>
+        <v>279</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="8" t="s">
-        <v>194</v>
+        <v>280</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="8" t="s">
-        <v>195</v>
+        <v>281</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="8" t="s">
-        <v>196</v>
+        <v>130</v>
       </c>
     </row>
     <row r="252" spans="1:1">
-      <c r="A252" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1" ht="15">
-      <c r="A254" s="11" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1">
-      <c r="A256" s="8" t="s">
-        <v>198</v>
+      <c r="A252" s="9"/>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" ht="15">
+      <c r="A256" s="11" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="257" spans="1:1">
-      <c r="A257" s="8" t="s">
-        <v>199</v>
-      </c>
+      <c r="A257" s="9"/>
     </row>
     <row r="258" spans="1:1">
-      <c r="A258" s="8" t="s">
-        <v>200</v>
+      <c r="A258" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="259" spans="1:1">
-      <c r="A259" s="8" t="s">
-        <v>201</v>
+      <c r="A259" s="9" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="260" spans="1:1">
-      <c r="A260" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1">
-      <c r="A261" s="8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1">
-      <c r="A262" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1" ht="15">
-      <c r="A264" s="7" t="s">
-        <v>204</v>
+      <c r="A260" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" ht="15">
+      <c r="A262" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="8" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="8" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="8" t="s">
-        <v>205</v>
+        <v>290</v>
       </c>
     </row>
     <row r="267" spans="1:1">
-      <c r="A267" s="8" t="s">
-        <v>206</v>
-      </c>
+      <c r="A267" s="9"/>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="8" t="s">
-        <v>207</v>
+        <v>291</v>
       </c>
     </row>
     <row r="269" spans="1:1">
-      <c r="A269" s="9"/>
+      <c r="A269" s="8" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="270" spans="1:1">
-      <c r="A270" s="8" t="s">
-        <v>208</v>
-      </c>
+      <c r="A270" s="9"/>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="8" t="s">
-        <v>209</v>
+        <v>293</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" s="8" t="s">
-        <v>210</v>
+        <v>294</v>
       </c>
     </row>
     <row r="273" spans="1:1">
-      <c r="A273" s="8" t="s">
-        <v>211</v>
-      </c>
+      <c r="A273" s="9"/>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="8" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="276" spans="1:1" ht="15">
-      <c r="A276" s="7" t="s">
-        <v>213</v>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="8" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="9"/>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="8" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" s="8" t="s">
-        <v>214</v>
+        <v>298</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="8" t="s">
-        <v>215</v>
+        <v>299</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="8" t="s">
-        <v>216</v>
+        <v>300</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="282" spans="1:1">
-      <c r="A282" s="9"/>
-    </row>
     <row r="283" spans="1:1">
-      <c r="A283" s="8" t="s">
-        <v>217</v>
-      </c>
+      <c r="A283" s="9"/>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="8" t="s">
-        <v>218</v>
+        <v>301</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" s="8" t="s">
-        <v>219</v>
+        <v>302</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="287" spans="1:1">
-      <c r="A287" s="9"/>
-    </row>
-    <row r="288" spans="1:1">
-      <c r="A288" s="8" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="289" spans="1:1">
-      <c r="A289" s="8" t="s">
-        <v>221</v>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" ht="15">
+      <c r="A288" s="7" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" s="8" t="s">
-        <v>222</v>
+        <v>305</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="8" t="s">
-        <v>223</v>
+        <v>306</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="296" spans="1:1" ht="15">
-      <c r="A296" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="298" spans="1:1" ht="15">
-      <c r="A298" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="300" spans="1:1" ht="15">
-      <c r="A300" s="7" t="s">
-        <v>226</v>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" s="9"/>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" s="8" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" s="8" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" s="9"/>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" s="8" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" s="8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" s="8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" s="8" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" s="8" t="s">
-        <v>227</v>
+        <v>315</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" s="8" t="s">
-        <v>228</v>
+        <v>316</v>
       </c>
     </row>
     <row r="304" spans="1:1">
@@ -4242,22 +4857,22 @@
     </row>
     <row r="305" spans="1:1">
       <c r="A305" s="8" t="s">
-        <v>229</v>
+        <v>317</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" s="8" t="s">
-        <v>230</v>
+        <v>143</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" s="8" t="s">
-        <v>231</v>
+        <v>318</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" s="8" t="s">
-        <v>130</v>
+        <v>319</v>
       </c>
     </row>
     <row r="309" spans="1:1">
@@ -4265,37 +4880,37 @@
     </row>
     <row r="310" spans="1:1">
       <c r="A310" s="8" t="s">
-        <v>232</v>
+        <v>320</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" s="8" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="313" spans="1:1" ht="15">
-      <c r="A313" s="7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="315" spans="1:1">
-      <c r="A315" s="8" t="s">
-        <v>235</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312" s="8" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" ht="15">
+      <c r="A314" s="11" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="316" spans="1:1">
       <c r="A316" s="8" t="s">
-        <v>236</v>
+        <v>324</v>
       </c>
     </row>
     <row r="317" spans="1:1">
       <c r="A317" s="8" t="s">
-        <v>237</v>
+        <v>325</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" s="8" t="s">
-        <v>130</v>
+        <v>326</v>
       </c>
     </row>
     <row r="319" spans="1:1">
@@ -4303,45 +4918,35 @@
     </row>
     <row r="320" spans="1:1">
       <c r="A320" s="8" t="s">
-        <v>238</v>
+        <v>327</v>
       </c>
     </row>
     <row r="321" spans="1:1">
       <c r="A321" s="8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="322" spans="1:1">
-      <c r="A322" s="8" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="323" spans="1:1">
-      <c r="A323" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="324" spans="1:1">
-      <c r="A324" s="9"/>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" ht="15">
+      <c r="A323" s="7" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325" s="8" t="s">
-        <v>241</v>
+        <v>330</v>
       </c>
     </row>
     <row r="326" spans="1:1">
-      <c r="A326" s="8" t="s">
-        <v>242</v>
-      </c>
+      <c r="A326" s="9"/>
     </row>
     <row r="327" spans="1:1">
       <c r="A327" s="8" t="s">
-        <v>243</v>
+        <v>331</v>
       </c>
     </row>
     <row r="328" spans="1:1">
       <c r="A328" s="8" t="s">
-        <v>130</v>
+        <v>332</v>
       </c>
     </row>
     <row r="329" spans="1:1">
@@ -4349,27 +4954,25 @@
     </row>
     <row r="330" spans="1:1">
       <c r="A330" s="8" t="s">
-        <v>244</v>
+        <v>333</v>
       </c>
     </row>
     <row r="331" spans="1:1">
       <c r="A331" s="8" t="s">
-        <v>245</v>
+        <v>334</v>
       </c>
     </row>
     <row r="332" spans="1:1">
-      <c r="A332" s="8" t="s">
-        <v>246</v>
-      </c>
+      <c r="A332" s="9"/>
     </row>
     <row r="333" spans="1:1">
       <c r="A333" s="8" t="s">
-        <v>247</v>
+        <v>335</v>
       </c>
     </row>
     <row r="334" spans="1:1">
       <c r="A334" s="8" t="s">
-        <v>248</v>
+        <v>336</v>
       </c>
     </row>
     <row r="335" spans="1:1">
@@ -4377,539 +4980,538 @@
     </row>
     <row r="336" spans="1:1">
       <c r="A336" s="8" t="s">
-        <v>249</v>
+        <v>337</v>
       </c>
     </row>
     <row r="337" spans="1:1">
       <c r="A337" s="8" t="s">
-        <v>250</v>
+        <v>338</v>
       </c>
     </row>
     <row r="338" spans="1:1">
       <c r="A338" s="8" t="s">
-        <v>251</v>
+        <v>339</v>
       </c>
     </row>
     <row r="339" spans="1:1">
       <c r="A339" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="341" spans="1:1" ht="15">
-      <c r="A341" s="11" t="s">
-        <v>100</v>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" s="8" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" s="8" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="342" spans="1:1">
-      <c r="A342" s="9"/>
+      <c r="A342" s="8" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="343" spans="1:1">
-      <c r="A343" s="9" t="s">
-        <v>252</v>
+      <c r="A343" s="8" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="344" spans="1:1">
-      <c r="A344" s="9" t="s">
-        <v>253</v>
+      <c r="A344" s="8" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="345" spans="1:1">
-      <c r="A345" s="9" t="s">
-        <v>254</v>
+      <c r="A345" s="8" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="346" spans="1:1">
-      <c r="A346" s="9" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="348" spans="1:1" ht="15">
-      <c r="A348" s="7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="350" spans="1:1">
-      <c r="A350" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="351" spans="1:1">
-      <c r="A351" s="8" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="352" spans="1:1">
-      <c r="A352" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="353" spans="1:1">
-      <c r="A353" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="354" spans="1:1">
-      <c r="A354" s="9"/>
-    </row>
-    <row r="355" spans="1:1">
-      <c r="A355" s="8" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="356" spans="1:1">
-      <c r="A356" s="8" t="s">
-        <v>261</v>
+      <c r="A346" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" s="8" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" ht="15">
+      <c r="A351" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" ht="15">
+      <c r="A353" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" ht="15">
+      <c r="A355" s="7" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="357" spans="1:1">
-      <c r="A357" s="9"/>
+      <c r="A357" s="8" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="358" spans="1:1">
       <c r="A358" s="8" t="s">
-        <v>262</v>
+        <v>351</v>
       </c>
     </row>
     <row r="359" spans="1:1">
       <c r="A359" s="8" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="361" spans="1:1" ht="15">
-      <c r="A361" s="7" t="s">
-        <v>264</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360" s="8" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361" s="9"/>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362" s="8" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="363" spans="1:1">
       <c r="A363" s="8" t="s">
-        <v>265</v>
+        <v>355</v>
       </c>
     </row>
     <row r="364" spans="1:1">
       <c r="A364" s="8" t="s">
-        <v>266</v>
+        <v>356</v>
       </c>
     </row>
     <row r="365" spans="1:1">
-      <c r="A365" s="8" t="s">
-        <v>267</v>
-      </c>
+      <c r="A365" s="9"/>
     </row>
     <row r="366" spans="1:1">
       <c r="A366" s="8" t="s">
-        <v>268</v>
+        <v>357</v>
       </c>
     </row>
     <row r="367" spans="1:1">
-      <c r="A367" s="9"/>
-    </row>
-    <row r="368" spans="1:1">
-      <c r="A368" s="8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="369" spans="1:1">
-      <c r="A369" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="370" spans="1:1">
-      <c r="A370" s="8" t="s">
-        <v>271</v>
+      <c r="A367" s="8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" ht="15">
+      <c r="A369" s="7" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="371" spans="1:1">
       <c r="A371" s="8" t="s">
-        <v>272</v>
+        <v>360</v>
       </c>
     </row>
     <row r="372" spans="1:1">
-      <c r="A372" s="9"/>
+      <c r="A372" s="8" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="373" spans="1:1">
       <c r="A373" s="8" t="s">
-        <v>273</v>
+        <v>362</v>
       </c>
     </row>
     <row r="374" spans="1:1">
       <c r="A374" s="8" t="s">
-        <v>274</v>
+        <v>363</v>
       </c>
     </row>
     <row r="375" spans="1:1">
-      <c r="A375" s="8" t="s">
-        <v>275</v>
-      </c>
+      <c r="A375" s="9"/>
     </row>
     <row r="376" spans="1:1">
       <c r="A376" s="8" t="s">
-        <v>276</v>
+        <v>364</v>
       </c>
     </row>
     <row r="377" spans="1:1">
       <c r="A377" s="8" t="s">
-        <v>277</v>
+        <v>365</v>
       </c>
     </row>
     <row r="378" spans="1:1">
       <c r="A378" s="8" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="382" spans="1:1" ht="15">
-      <c r="A382" s="7" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="384" spans="1:1" ht="15">
-      <c r="A384" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="386" spans="1:1">
-      <c r="A386" s="8" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="387" spans="1:1">
-      <c r="A387" s="8" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="388" spans="1:1">
-      <c r="A388" s="8" t="s">
-        <v>283</v>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" s="9"/>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" s="8" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" s="9"/>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" s="8" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" s="8" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" ht="15">
+      <c r="A387" s="7" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="389" spans="1:1">
       <c r="A389" s="8" t="s">
-        <v>130</v>
+        <v>372</v>
       </c>
     </row>
     <row r="390" spans="1:1">
-      <c r="A390" s="9"/>
+      <c r="A390" s="8" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="391" spans="1:1">
-      <c r="A391" s="8" t="s">
-        <v>284</v>
-      </c>
+      <c r="A391" s="9"/>
     </row>
     <row r="392" spans="1:1">
       <c r="A392" s="8" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="394" spans="1:1" ht="15">
-      <c r="A394" s="11" t="s">
-        <v>286</v>
+        <v>374</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" s="8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394" s="8" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="395" spans="1:1">
-      <c r="A395" s="9"/>
+      <c r="A395" s="8" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="396" spans="1:1">
-      <c r="A396" s="9" t="s">
-        <v>287</v>
+      <c r="A396" s="8" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="397" spans="1:1">
-      <c r="A397" s="9" t="s">
-        <v>288</v>
-      </c>
+      <c r="A397" s="9"/>
     </row>
     <row r="398" spans="1:1">
-      <c r="A398" s="9" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="400" spans="1:1" ht="15">
-      <c r="A400" s="7" t="s">
-        <v>290</v>
+      <c r="A398" s="8" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399" s="8" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400" s="9"/>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401" s="8" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="402" spans="1:1">
       <c r="A402" s="8" t="s">
-        <v>291</v>
+        <v>380</v>
       </c>
     </row>
     <row r="403" spans="1:1">
       <c r="A403" s="8" t="s">
-        <v>266</v>
+        <v>381</v>
       </c>
     </row>
     <row r="404" spans="1:1">
       <c r="A404" s="8" t="s">
-        <v>292</v>
+        <v>382</v>
       </c>
     </row>
     <row r="405" spans="1:1">
-      <c r="A405" s="9"/>
+      <c r="A405" s="8" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="406" spans="1:1">
-      <c r="A406" s="8" t="s">
-        <v>293</v>
-      </c>
+      <c r="A406" s="9"/>
     </row>
     <row r="407" spans="1:1">
       <c r="A407" s="8" t="s">
-        <v>294</v>
+        <v>383</v>
       </c>
     </row>
     <row r="408" spans="1:1">
-      <c r="A408" s="9"/>
+      <c r="A408" s="8" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="409" spans="1:1">
       <c r="A409" s="8" t="s">
-        <v>295</v>
+        <v>384</v>
       </c>
     </row>
     <row r="410" spans="1:1">
       <c r="A410" s="8" t="s">
-        <v>296</v>
+        <v>130</v>
       </c>
     </row>
     <row r="411" spans="1:1">
-      <c r="A411" s="9"/>
+      <c r="A411" s="8" t="s">
+        <v>385</v>
+      </c>
     </row>
     <row r="412" spans="1:1">
-      <c r="A412" s="8" t="s">
-        <v>297</v>
-      </c>
+      <c r="A412" s="9"/>
     </row>
     <row r="413" spans="1:1">
       <c r="A413" s="8" t="s">
-        <v>298</v>
+        <v>386</v>
       </c>
     </row>
     <row r="414" spans="1:1">
-      <c r="A414" s="9"/>
-    </row>
-    <row r="415" spans="1:1">
-      <c r="A415" s="8" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="416" spans="1:1">
-      <c r="A416" s="8" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="417" spans="1:1">
-      <c r="A417" s="8" t="s">
-        <v>301</v>
+      <c r="A414" s="8" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" ht="15">
+      <c r="A416" s="7" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="418" spans="1:1">
       <c r="A418" s="8" t="s">
-        <v>302</v>
+        <v>389</v>
       </c>
     </row>
     <row r="419" spans="1:1">
-      <c r="A419" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="A419" s="9"/>
     </row>
     <row r="420" spans="1:1">
       <c r="A420" s="8" t="s">
-        <v>130</v>
+        <v>390</v>
       </c>
     </row>
     <row r="421" spans="1:1">
-      <c r="A421" s="9"/>
+      <c r="A421" s="8" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="422" spans="1:1">
       <c r="A422" s="8" t="s">
-        <v>303</v>
+        <v>392</v>
       </c>
     </row>
     <row r="423" spans="1:1">
       <c r="A423" s="8" t="s">
-        <v>304</v>
+        <v>393</v>
       </c>
     </row>
     <row r="424" spans="1:1">
       <c r="A424" s="8" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="426" spans="1:1" ht="15">
-      <c r="A426" s="7" t="s">
-        <v>306</v>
-      </c>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425" s="9"/>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426" s="8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427" s="9"/>
     </row>
     <row r="428" spans="1:1">
       <c r="A428" s="8" t="s">
-        <v>307</v>
+        <v>395</v>
       </c>
     </row>
     <row r="429" spans="1:1">
       <c r="A429" s="8" t="s">
-        <v>308</v>
+        <v>396</v>
       </c>
     </row>
     <row r="430" spans="1:1">
       <c r="A430" s="8" t="s">
-        <v>309</v>
+        <v>397</v>
       </c>
     </row>
     <row r="431" spans="1:1">
-      <c r="A431" s="9"/>
+      <c r="A431" s="8" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="432" spans="1:1">
       <c r="A432" s="8" t="s">
-        <v>310</v>
+        <v>130</v>
       </c>
     </row>
     <row r="433" spans="1:1">
-      <c r="A433" s="8" t="s">
-        <v>311</v>
-      </c>
+      <c r="A433" s="9"/>
     </row>
     <row r="434" spans="1:1">
       <c r="A434" s="8" t="s">
-        <v>312</v>
+        <v>399</v>
       </c>
     </row>
     <row r="435" spans="1:1">
-      <c r="A435" s="9"/>
+      <c r="A435" s="8" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="436" spans="1:1">
       <c r="A436" s="8" t="s">
-        <v>313</v>
+        <v>401</v>
       </c>
     </row>
     <row r="437" spans="1:1">
       <c r="A437" s="8" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="438" spans="1:1">
-      <c r="A438" s="8" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="439" spans="1:1">
-      <c r="A439" s="8" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="440" spans="1:1">
-      <c r="A440" s="8" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="441" spans="1:1">
-      <c r="A441" s="8" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="442" spans="1:1">
-      <c r="A442" s="9"/>
-    </row>
-    <row r="443" spans="1:1">
-      <c r="A443" s="8" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="444" spans="1:1">
-      <c r="A444" s="8" t="s">
-        <v>143</v>
+        <v>402</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" ht="15">
+      <c r="A441" s="7" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" ht="15">
+      <c r="A443" s="7" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="445" spans="1:1">
       <c r="A445" s="8" t="s">
-        <v>320</v>
+        <v>405</v>
       </c>
     </row>
     <row r="446" spans="1:1">
       <c r="A446" s="8" t="s">
-        <v>321</v>
+        <v>406</v>
       </c>
     </row>
     <row r="447" spans="1:1">
-      <c r="A447" s="9"/>
+      <c r="A447" s="8" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="448" spans="1:1">
       <c r="A448" s="8" t="s">
-        <v>322</v>
+        <v>408</v>
       </c>
     </row>
     <row r="449" spans="1:1">
-      <c r="A449" s="8" t="s">
-        <v>323</v>
-      </c>
+      <c r="A449" s="9"/>
     </row>
     <row r="450" spans="1:1">
       <c r="A450" s="8" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="452" spans="1:1" ht="15">
-      <c r="A452" s="11" t="s">
-        <v>325</v>
+        <v>409</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451" s="8" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452" s="8" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453" s="8" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="454" spans="1:1">
       <c r="A454" s="8" t="s">
-        <v>326</v>
+        <v>413</v>
       </c>
     </row>
     <row r="455" spans="1:1">
-      <c r="A455" s="8" t="s">
-        <v>327</v>
-      </c>
+      <c r="A455" s="9"/>
     </row>
     <row r="456" spans="1:1">
       <c r="A456" s="8" t="s">
-        <v>328</v>
+        <v>414</v>
       </c>
     </row>
     <row r="457" spans="1:1">
-      <c r="A457" s="9"/>
+      <c r="A457" s="8" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="458" spans="1:1">
       <c r="A458" s="8" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="459" spans="1:1">
-      <c r="A459" s="8" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="461" spans="1:1" ht="15">
-      <c r="A461" s="7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="463" spans="1:1">
-      <c r="A463" s="8" t="s">
-        <v>332</v>
+        <v>416</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" ht="15">
+      <c r="A460" s="11" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" ht="15">
+      <c r="A462" s="7" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="464" spans="1:1">
-      <c r="A464" s="9"/>
+      <c r="A464" s="8" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="465" spans="1:1">
-      <c r="A465" s="8" t="s">
-        <v>333</v>
-      </c>
+      <c r="A465" s="9"/>
     </row>
     <row r="466" spans="1:1">
       <c r="A466" s="8" t="s">
-        <v>334</v>
+        <v>374</v>
       </c>
     </row>
     <row r="467" spans="1:1">
-      <c r="A467" s="9"/>
+      <c r="A467" s="8" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="468" spans="1:1">
       <c r="A468" s="8" t="s">
-        <v>335</v>
+        <v>420</v>
       </c>
     </row>
     <row r="469" spans="1:1">
       <c r="A469" s="8" t="s">
-        <v>336</v>
+        <v>421</v>
       </c>
     </row>
     <row r="470" spans="1:1">
@@ -4917,1040 +5519,811 @@
     </row>
     <row r="471" spans="1:1">
       <c r="A471" s="8" t="s">
-        <v>337</v>
+        <v>422</v>
       </c>
     </row>
     <row r="472" spans="1:1">
       <c r="A472" s="8" t="s">
-        <v>338</v>
+        <v>423</v>
       </c>
     </row>
     <row r="473" spans="1:1">
-      <c r="A473" s="9"/>
+      <c r="A473" s="8" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="474" spans="1:1">
-      <c r="A474" s="8" t="s">
-        <v>339</v>
-      </c>
+      <c r="A474" s="9"/>
     </row>
     <row r="475" spans="1:1">
       <c r="A475" s="8" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
     </row>
     <row r="476" spans="1:1">
       <c r="A476" s="8" t="s">
-        <v>341</v>
+        <v>425</v>
       </c>
     </row>
     <row r="477" spans="1:1">
       <c r="A477" s="8" t="s">
-        <v>342</v>
+        <v>426</v>
       </c>
     </row>
     <row r="478" spans="1:1">
       <c r="A478" s="8" t="s">
-        <v>343</v>
+        <v>427</v>
       </c>
     </row>
     <row r="479" spans="1:1">
-      <c r="A479" s="8" t="s">
-        <v>344</v>
-      </c>
+      <c r="A479" s="9"/>
     </row>
     <row r="480" spans="1:1">
       <c r="A480" s="8" t="s">
-        <v>173</v>
+        <v>428</v>
       </c>
     </row>
     <row r="481" spans="1:1">
       <c r="A481" s="8" t="s">
-        <v>345</v>
+        <v>429</v>
       </c>
     </row>
     <row r="482" spans="1:1">
       <c r="A482" s="8" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="483" spans="1:1">
-      <c r="A483" s="8" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="484" spans="1:1">
-      <c r="A484" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="485" spans="1:1">
-      <c r="A485" s="8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="489" spans="1:1" ht="15">
-      <c r="A489" s="7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="491" spans="1:1" ht="15">
-      <c r="A491" s="7" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="493" spans="1:1" ht="15">
-      <c r="A493" s="7" t="s">
-        <v>351</v>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" ht="15">
+      <c r="A484" s="7" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1">
+      <c r="A486" s="8" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1">
+      <c r="A487" s="9"/>
+    </row>
+    <row r="488" spans="1:1">
+      <c r="A488" s="8" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1">
+      <c r="A489" s="8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1">
+      <c r="A490" s="8" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1">
+      <c r="A491" s="8" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1">
+      <c r="A492" s="9"/>
+    </row>
+    <row r="493" spans="1:1">
+      <c r="A493" s="8" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1">
+      <c r="A494" s="8" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="495" spans="1:1">
       <c r="A495" s="8" t="s">
-        <v>352</v>
+        <v>439</v>
       </c>
     </row>
     <row r="496" spans="1:1">
-      <c r="A496" s="8" t="s">
-        <v>353</v>
-      </c>
+      <c r="A496" s="9"/>
     </row>
     <row r="497" spans="1:1">
       <c r="A497" s="8" t="s">
-        <v>354</v>
+        <v>440</v>
       </c>
     </row>
     <row r="498" spans="1:1">
       <c r="A498" s="8" t="s">
-        <v>355</v>
+        <v>441</v>
       </c>
     </row>
     <row r="499" spans="1:1">
-      <c r="A499" s="9"/>
+      <c r="A499" s="8" t="s">
+        <v>442</v>
+      </c>
     </row>
     <row r="500" spans="1:1">
       <c r="A500" s="8" t="s">
-        <v>356</v>
+        <v>443</v>
       </c>
     </row>
     <row r="501" spans="1:1">
       <c r="A501" s="8" t="s">
-        <v>357</v>
+        <v>130</v>
       </c>
     </row>
     <row r="502" spans="1:1">
-      <c r="A502" s="8" t="s">
-        <v>358</v>
-      </c>
+      <c r="A502" s="9"/>
     </row>
     <row r="503" spans="1:1">
-      <c r="A503" s="9"/>
+      <c r="A503" s="8" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="504" spans="1:1">
-      <c r="A504" s="8" t="s">
-        <v>359</v>
-      </c>
+      <c r="A504" s="9"/>
     </row>
     <row r="505" spans="1:1">
       <c r="A505" s="8" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="507" spans="1:1" ht="15">
-      <c r="A507" s="7" t="s">
-        <v>361</v>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1">
+      <c r="A506" s="8" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1">
+      <c r="A507" s="9"/>
+    </row>
+    <row r="508" spans="1:1">
+      <c r="A508" s="8" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="509" spans="1:1">
       <c r="A509" s="8" t="s">
-        <v>362</v>
+        <v>448</v>
       </c>
     </row>
     <row r="510" spans="1:1">
       <c r="A510" s="8" t="s">
-        <v>363</v>
+        <v>449</v>
       </c>
     </row>
     <row r="511" spans="1:1">
-      <c r="A511" s="8" t="s">
-        <v>364</v>
-      </c>
+      <c r="A511" s="9"/>
     </row>
     <row r="512" spans="1:1">
       <c r="A512" s="8" t="s">
-        <v>365</v>
+        <v>450</v>
       </c>
     </row>
     <row r="513" spans="1:1">
-      <c r="A513" s="9"/>
+      <c r="A513" s="8" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="514" spans="1:1">
       <c r="A514" s="8" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="515" spans="1:1">
-      <c r="A515" s="8" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="516" spans="1:1">
-      <c r="A516" s="8" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="517" spans="1:1">
-      <c r="A517" s="8" t="s">
-        <v>130</v>
+        <v>452</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1" ht="15">
+      <c r="A516" s="7" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="518" spans="1:1">
-      <c r="A518" s="9"/>
+      <c r="A518" s="8" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="519" spans="1:1">
       <c r="A519" s="8" t="s">
-        <v>369</v>
+        <v>455</v>
       </c>
     </row>
     <row r="520" spans="1:1">
-      <c r="A520" s="8" t="s">
-        <v>370</v>
-      </c>
+      <c r="A520" s="9"/>
     </row>
     <row r="521" spans="1:1">
-      <c r="A521" s="9"/>
+      <c r="A521" s="8" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="522" spans="1:1">
       <c r="A522" s="8" t="s">
-        <v>371</v>
+        <v>457</v>
       </c>
     </row>
     <row r="523" spans="1:1">
-      <c r="A523" s="8" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="525" spans="1:1" ht="15">
-      <c r="A525" s="7" t="s">
-        <v>373</v>
+      <c r="A523" s="9"/>
+    </row>
+    <row r="524" spans="1:1">
+      <c r="A524" s="8" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1">
+      <c r="A525" s="8" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1">
+      <c r="A526" s="8" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="527" spans="1:1">
       <c r="A527" s="8" t="s">
-        <v>374</v>
+        <v>461</v>
       </c>
     </row>
     <row r="528" spans="1:1">
       <c r="A528" s="8" t="s">
-        <v>375</v>
+        <v>462</v>
       </c>
     </row>
     <row r="529" spans="1:1">
-      <c r="A529" s="9"/>
+      <c r="A529" s="8" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="530" spans="1:1">
       <c r="A530" s="8" t="s">
-        <v>376</v>
+        <v>463</v>
       </c>
     </row>
     <row r="531" spans="1:1">
-      <c r="A531" s="8" t="s">
-        <v>377</v>
-      </c>
+      <c r="A531" s="9"/>
     </row>
     <row r="532" spans="1:1">
       <c r="A532" s="8" t="s">
-        <v>378</v>
+        <v>464</v>
       </c>
     </row>
     <row r="533" spans="1:1">
       <c r="A533" s="8" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="534" spans="1:1">
-      <c r="A534" s="8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="535" spans="1:1">
-      <c r="A535" s="9"/>
-    </row>
-    <row r="536" spans="1:1">
-      <c r="A536" s="8" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="537" spans="1:1">
-      <c r="A537" s="8" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="538" spans="1:1">
-      <c r="A538" s="9"/>
-    </row>
-    <row r="539" spans="1:1">
-      <c r="A539" s="8" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="540" spans="1:1">
-      <c r="A540" s="8" t="s">
-        <v>382</v>
-      </c>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1" ht="15">
+      <c r="A537" s="7"/>
+    </row>
+    <row r="539" spans="1:1" ht="15">
+      <c r="A539" s="7"/>
     </row>
     <row r="541" spans="1:1">
-      <c r="A541" s="8" t="s">
-        <v>383</v>
-      </c>
+      <c r="A541" s="8"/>
     </row>
     <row r="542" spans="1:1">
-      <c r="A542" s="8" t="s">
-        <v>384</v>
-      </c>
+      <c r="A542" s="8"/>
     </row>
     <row r="543" spans="1:1">
-      <c r="A543" s="8" t="s">
-        <v>130</v>
-      </c>
+      <c r="A543" s="8"/>
     </row>
     <row r="544" spans="1:1">
       <c r="A544" s="9"/>
     </row>
     <row r="545" spans="1:1">
-      <c r="A545" s="8" t="s">
-        <v>385</v>
-      </c>
+      <c r="A545" s="8"/>
     </row>
     <row r="546" spans="1:1">
-      <c r="A546" s="8" t="s">
-        <v>383</v>
-      </c>
+      <c r="A546" s="8"/>
     </row>
     <row r="547" spans="1:1">
-      <c r="A547" s="8" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="548" spans="1:1">
-      <c r="A548" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="549" spans="1:1">
-      <c r="A549" s="8" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="550" spans="1:1">
-      <c r="A550" s="9"/>
+      <c r="A547" s="8"/>
+    </row>
+    <row r="549" spans="1:1" ht="15">
+      <c r="A549" s="7"/>
     </row>
     <row r="551" spans="1:1">
-      <c r="A551" s="8" t="s">
-        <v>388</v>
-      </c>
+      <c r="A551" s="8"/>
     </row>
     <row r="552" spans="1:1">
-      <c r="A552" s="8" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="554" spans="1:1" ht="15">
-      <c r="A554" s="7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="556" spans="1:1">
-      <c r="A556" s="8" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="557" spans="1:1">
-      <c r="A557" s="9"/>
+      <c r="A552" s="8"/>
+    </row>
+    <row r="553" spans="1:1">
+      <c r="A553" s="9"/>
+    </row>
+    <row r="554" spans="1:1">
+      <c r="A554" s="8"/>
+    </row>
+    <row r="556" spans="1:1" ht="15">
+      <c r="A556" s="7"/>
     </row>
     <row r="558" spans="1:1">
-      <c r="A558" s="8" t="s">
-        <v>392</v>
-      </c>
+      <c r="A558" s="8"/>
     </row>
     <row r="559" spans="1:1">
-      <c r="A559" s="8" t="s">
-        <v>393</v>
-      </c>
+      <c r="A559" s="8"/>
     </row>
     <row r="560" spans="1:1">
-      <c r="A560" s="8" t="s">
-        <v>394</v>
-      </c>
+      <c r="A560" s="8"/>
     </row>
     <row r="561" spans="1:1">
-      <c r="A561" s="8" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="562" spans="1:1">
-      <c r="A562" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="563" spans="1:1">
-      <c r="A563" s="9"/>
-    </row>
-    <row r="564" spans="1:1">
-      <c r="A564" s="8" t="s">
-        <v>396</v>
-      </c>
+      <c r="A561" s="8"/>
+    </row>
+    <row r="563" spans="1:1" ht="15">
+      <c r="A563" s="7"/>
     </row>
     <row r="565" spans="1:1">
-      <c r="A565" s="9"/>
+      <c r="A565" s="8"/>
     </row>
     <row r="566" spans="1:1">
-      <c r="A566" s="8" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="567" spans="1:1">
-      <c r="A567" s="8" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="568" spans="1:1">
-      <c r="A568" s="8" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="569" spans="1:1">
-      <c r="A569" s="8" t="s">
-        <v>400</v>
-      </c>
+      <c r="A566" s="8"/>
+    </row>
+    <row r="568" spans="1:1" ht="15">
+      <c r="A568" s="7"/>
     </row>
     <row r="570" spans="1:1">
-      <c r="A570" s="8" t="s">
-        <v>130</v>
-      </c>
+      <c r="A570" s="8"/>
     </row>
     <row r="571" spans="1:1">
-      <c r="A571" s="9"/>
+      <c r="A571" s="8"/>
     </row>
     <row r="572" spans="1:1">
-      <c r="A572" s="8" t="s">
-        <v>401</v>
-      </c>
+      <c r="A572" s="9"/>
     </row>
     <row r="573" spans="1:1">
-      <c r="A573" s="8" t="s">
-        <v>402</v>
-      </c>
+      <c r="A573" s="8"/>
     </row>
     <row r="574" spans="1:1">
-      <c r="A574" s="8" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="575" spans="1:1">
-      <c r="A575" s="8" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="579" spans="1:1" ht="15">
-      <c r="A579" s="7" t="s">
-        <v>405</v>
-      </c>
+      <c r="A574" s="8"/>
+    </row>
+    <row r="578" spans="1:1" ht="15">
+      <c r="A578" s="7"/>
+    </row>
+    <row r="579" spans="1:1">
+      <c r="A579" s="9"/>
+    </row>
+    <row r="580" spans="1:1" ht="15">
+      <c r="A580" s="7"/>
     </row>
     <row r="581" spans="1:1" ht="15">
-      <c r="A581" s="7" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="583" spans="1:1">
-      <c r="A583" s="8" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="584" spans="1:1">
-      <c r="A584" s="8" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="585" spans="1:1">
-      <c r="A585" s="8" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="586" spans="1:1">
-      <c r="A586" s="8" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="587" spans="1:1">
-      <c r="A587" s="9"/>
-    </row>
-    <row r="588" spans="1:1">
-      <c r="A588" s="8" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="589" spans="1:1">
-      <c r="A589" s="8" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="590" spans="1:1">
-      <c r="A590" s="8" t="s">
-        <v>413</v>
-      </c>
+      <c r="A581" s="7"/>
+    </row>
+    <row r="582" spans="1:1" ht="15">
+      <c r="A582" s="7"/>
+    </row>
+    <row r="583" spans="1:1" ht="15">
+      <c r="A583" s="7"/>
+    </row>
+    <row r="584" spans="1:1" ht="15">
+      <c r="A584" s="7"/>
+    </row>
+    <row r="585" spans="1:1" ht="15">
+      <c r="A585" s="7"/>
+    </row>
+    <row r="586" spans="1:1" ht="15">
+      <c r="A586" s="7"/>
+    </row>
+    <row r="590" spans="1:1" ht="15">
+      <c r="A590" s="11"/>
     </row>
     <row r="591" spans="1:1">
-      <c r="A591" s="8" t="s">
-        <v>414</v>
-      </c>
+      <c r="A591" s="9"/>
     </row>
     <row r="592" spans="1:1">
-      <c r="A592" s="8" t="s">
-        <v>415</v>
-      </c>
+      <c r="A592" s="9"/>
     </row>
     <row r="593" spans="1:1">
       <c r="A593" s="9"/>
     </row>
     <row r="594" spans="1:1">
-      <c r="A594" s="8" t="s">
-        <v>416</v>
-      </c>
+      <c r="A594" s="9"/>
     </row>
     <row r="595" spans="1:1">
-      <c r="A595" s="8" t="s">
-        <v>417</v>
-      </c>
+      <c r="A595" s="9"/>
     </row>
     <row r="596" spans="1:1">
-      <c r="A596" s="8" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="598" spans="1:1" ht="15">
-      <c r="A598" s="11" t="s">
+      <c r="A596" s="9"/>
+    </row>
+    <row r="597" spans="1:1">
+      <c r="A597" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BY33"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="16384" width="3" style="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:77" ht="15">
+      <c r="A1" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="U1" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
+      <c r="AC1" s="27"/>
+      <c r="AD1" s="27"/>
+      <c r="AE1" s="27"/>
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="27"/>
+      <c r="AH1" s="27"/>
+      <c r="AI1" s="27"/>
+      <c r="AJ1" s="27"/>
+      <c r="AK1" s="27"/>
+      <c r="AQ1" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="AR1" s="27"/>
+      <c r="AS1" s="27"/>
+      <c r="AT1" s="27"/>
+      <c r="AU1" s="27"/>
+      <c r="AV1" s="27"/>
+      <c r="AW1" s="27"/>
+      <c r="AX1" s="27"/>
+      <c r="AY1" s="27"/>
+      <c r="AZ1" s="27"/>
+      <c r="BA1" s="27"/>
+      <c r="BB1" s="27"/>
+      <c r="BC1" s="27"/>
+      <c r="BD1" s="27"/>
+      <c r="BE1" s="27"/>
+      <c r="BF1" s="27"/>
+      <c r="BG1" s="27"/>
+      <c r="BH1" s="27"/>
+      <c r="BK1" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="BL1" s="27"/>
+      <c r="BM1" s="27"/>
+      <c r="BN1" s="27"/>
+      <c r="BO1" s="27"/>
+      <c r="BP1" s="27"/>
+      <c r="BQ1" s="27"/>
+      <c r="BR1" s="27"/>
+      <c r="BS1" s="27"/>
+      <c r="BT1" s="27"/>
+      <c r="BU1" s="27"/>
+      <c r="BV1" s="27"/>
+      <c r="BW1" s="27"/>
+      <c r="BX1" s="27"/>
+      <c r="BY1" s="27"/>
+    </row>
+    <row r="2" spans="1:77" ht="15">
+      <c r="A2" s="22" t="s">
+        <v>551</v>
+      </c>
+      <c r="U2" s="22" t="s">
+        <v>494</v>
+      </c>
+      <c r="AQ2" s="22" t="s">
+        <v>553</v>
+      </c>
+      <c r="BK2" s="14" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3" spans="1:77" ht="15">
+      <c r="A3" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="AQ3" s="9" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="600" spans="1:1" ht="15">
-      <c r="A600" s="7" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="602" spans="1:1">
-      <c r="A602" s="8" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="603" spans="1:1">
-      <c r="A603" s="9"/>
-    </row>
-    <row r="604" spans="1:1">
-      <c r="A604" s="8" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="605" spans="1:1">
-      <c r="A605" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="606" spans="1:1">
-      <c r="A606" s="8" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="607" spans="1:1">
-      <c r="A607" s="8" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="608" spans="1:1">
-      <c r="A608" s="9"/>
-    </row>
-    <row r="609" spans="1:1">
-      <c r="A609" s="8" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="610" spans="1:1">
-      <c r="A610" s="8" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="611" spans="1:1">
-      <c r="A611" s="8" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="612" spans="1:1">
-      <c r="A612" s="9"/>
-    </row>
-    <row r="613" spans="1:1">
-      <c r="A613" s="8" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="614" spans="1:1">
-      <c r="A614" s="8" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="615" spans="1:1">
-      <c r="A615" s="8" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="616" spans="1:1">
-      <c r="A616" s="8" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="617" spans="1:1">
-      <c r="A617" s="9"/>
-    </row>
-    <row r="618" spans="1:1">
-      <c r="A618" s="8" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="619" spans="1:1">
-      <c r="A619" s="8" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="620" spans="1:1">
-      <c r="A620" s="8" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="622" spans="1:1" ht="15">
-      <c r="A622" s="7" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="624" spans="1:1">
-      <c r="A624" s="8" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="625" spans="1:1">
-      <c r="A625" s="9"/>
-    </row>
-    <row r="626" spans="1:1">
-      <c r="A626" s="8" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="627" spans="1:1">
-      <c r="A627" s="8" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="628" spans="1:1">
-      <c r="A628" s="8" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="629" spans="1:1">
-      <c r="A629" s="8" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="630" spans="1:1">
-      <c r="A630" s="9"/>
-    </row>
-    <row r="631" spans="1:1">
-      <c r="A631" s="8" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="632" spans="1:1">
-      <c r="A632" s="8" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="633" spans="1:1">
-      <c r="A633" s="8" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="634" spans="1:1">
-      <c r="A634" s="9"/>
-    </row>
-    <row r="635" spans="1:1">
-      <c r="A635" s="8" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="636" spans="1:1">
-      <c r="A636" s="8" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="637" spans="1:1">
-      <c r="A637" s="8" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="638" spans="1:1">
-      <c r="A638" s="8" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="639" spans="1:1">
-      <c r="A639" s="8" t="s">
+      <c r="BK3" s="9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="4" spans="1:77" ht="15">
+      <c r="A4" s="25" t="s">
+        <v>559</v>
+      </c>
+      <c r="U4" s="28" t="s">
+        <v>560</v>
+      </c>
+      <c r="AQ4" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="BK4" s="9" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="5" spans="1:77" ht="15">
+      <c r="A5" s="24" t="s">
+        <v>552</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="AQ5" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="BK5" s="9"/>
+    </row>
+    <row r="6" spans="1:77">
+      <c r="V6" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="AQ6" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="BK6" s="9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="7" spans="1:77">
+      <c r="A7" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="AQ7" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="BK7" s="9" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="8" spans="1:77">
+      <c r="A8" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="V8" s="9"/>
+      <c r="AQ8" s="9"/>
+      <c r="BK8" s="24" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="9" spans="1:77">
+      <c r="A9" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="AQ9" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="BK9" s="24" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="10" spans="1:77">
+      <c r="A10" s="9"/>
+      <c r="V10" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="AQ10" s="9" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:77" ht="15">
+      <c r="A11" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="AQ11" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="BK11" s="14" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="12" spans="1:77" ht="15">
+      <c r="A12" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="U12" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="AQ12" s="9"/>
+      <c r="BK12" s="9" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="13" spans="1:77" ht="15">
+      <c r="A13" s="9"/>
+      <c r="U13" s="28" t="s">
+        <v>502</v>
+      </c>
+      <c r="AQ13" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="BK13" s="9" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="14" spans="1:77">
+      <c r="A14" s="26" t="s">
+        <v>491</v>
+      </c>
+      <c r="V14" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="AQ14" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="BK14" s="9" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="15" spans="1:77">
+      <c r="A15" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="V15" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="AQ15" s="9" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="16" spans="1:77" ht="15">
+      <c r="V16" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="AQ16" s="9"/>
+      <c r="BK16" s="22" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="17" spans="21:63" ht="15">
+      <c r="V17" s="9"/>
+      <c r="AP17" s="22"/>
+      <c r="AQ17" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="BK17" s="24" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="18" spans="21:63">
+      <c r="V18" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="AQ18" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="BK18" s="24" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="19" spans="21:63">
+      <c r="V19" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="AQ19" s="9" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="20" spans="21:63" ht="15">
+      <c r="AQ20" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="BK20" s="28" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="21" spans="21:63" ht="15">
+      <c r="U21" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="AQ21" s="9"/>
+      <c r="BK21" s="9" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="22" spans="21:63" ht="15">
+      <c r="U22" s="28" t="s">
+        <v>509</v>
+      </c>
+      <c r="AQ22" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="BK22" s="9" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="23" spans="21:63">
+      <c r="V23" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="AQ23" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="BK23" s="9"/>
+    </row>
+    <row r="24" spans="21:63">
+      <c r="V24" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="AQ24" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="BK24" s="9" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="25" spans="21:63">
+      <c r="AQ25" s="9" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="640" spans="1:1">
-      <c r="A640" s="9"/>
-    </row>
-    <row r="641" spans="1:1">
-      <c r="A641" s="8" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="642" spans="1:1">
-      <c r="A642" s="9"/>
-    </row>
-    <row r="643" spans="1:1">
-      <c r="A643" s="8" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="644" spans="1:1">
-      <c r="A644" s="8" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="645" spans="1:1">
-      <c r="A645" s="9"/>
-    </row>
-    <row r="646" spans="1:1">
-      <c r="A646" s="8" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="647" spans="1:1">
-      <c r="A647" s="8" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="648" spans="1:1">
-      <c r="A648" s="8" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="649" spans="1:1">
-      <c r="A649" s="9"/>
-    </row>
-    <row r="650" spans="1:1">
-      <c r="A650" s="8" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="651" spans="1:1">
-      <c r="A651" s="8" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="652" spans="1:1">
-      <c r="A652" s="8" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="654" spans="1:1" ht="15">
-      <c r="A654" s="7" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="656" spans="1:1">
-      <c r="A656" s="8" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="657" spans="1:1">
-      <c r="A657" s="8" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="658" spans="1:1">
-      <c r="A658" s="9"/>
-    </row>
-    <row r="659" spans="1:1">
-      <c r="A659" s="8" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="660" spans="1:1">
-      <c r="A660" s="8" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="661" spans="1:1">
-      <c r="A661" s="9"/>
-    </row>
-    <row r="662" spans="1:1">
-      <c r="A662" s="8" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="663" spans="1:1">
-      <c r="A663" s="8" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="664" spans="1:1">
-      <c r="A664" s="8" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="665" spans="1:1">
-      <c r="A665" s="8" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="666" spans="1:1">
-      <c r="A666" s="8" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="667" spans="1:1">
-      <c r="A667" s="8" t="s">
+      <c r="BK25" s="9" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="26" spans="21:63" ht="15">
+      <c r="AQ26" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="BK26" s="9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="21:63">
+      <c r="AQ27" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="BK27" s="9" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="28" spans="21:63">
+      <c r="AQ28" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="BK28" s="9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="668" spans="1:1">
-      <c r="A668" s="8" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="669" spans="1:1">
-      <c r="A669" s="9"/>
-    </row>
-    <row r="670" spans="1:1">
-      <c r="A670" s="8" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="671" spans="1:1">
-      <c r="A671" s="8" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="675" spans="1:1" ht="15">
-      <c r="A675" s="7" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="677" spans="1:1" ht="15">
-      <c r="A677" s="7" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="679" spans="1:1">
-      <c r="A679" s="8" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="680" spans="1:1">
-      <c r="A680" s="8" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="681" spans="1:1">
-      <c r="A681" s="8" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="682" spans="1:1">
-      <c r="A682" s="9"/>
-    </row>
-    <row r="683" spans="1:1">
-      <c r="A683" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="684" spans="1:1">
-      <c r="A684" s="8" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="685" spans="1:1">
-      <c r="A685" s="8" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="687" spans="1:1" ht="15">
-      <c r="A687" s="7" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="689" spans="1:1">
-      <c r="A689" s="8" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="690" spans="1:1">
-      <c r="A690" s="8" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="691" spans="1:1">
-      <c r="A691" s="9"/>
-    </row>
-    <row r="692" spans="1:1">
-      <c r="A692" s="8" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="694" spans="1:1" ht="15">
-      <c r="A694" s="7" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="696" spans="1:1">
-      <c r="A696" s="8" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="697" spans="1:1">
-      <c r="A697" s="8" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="698" spans="1:1">
-      <c r="A698" s="8" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="699" spans="1:1">
-      <c r="A699" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="701" spans="1:1" ht="15">
-      <c r="A701" s="7" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="703" spans="1:1">
-      <c r="A703" s="8" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="704" spans="1:1">
-      <c r="A704" s="8" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="706" spans="1:1" ht="15">
-      <c r="A706" s="7" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="708" spans="1:1">
-      <c r="A708" s="8" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="709" spans="1:1">
-      <c r="A709" s="8" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="710" spans="1:1">
-      <c r="A710" s="9"/>
-    </row>
-    <row r="711" spans="1:1">
-      <c r="A711" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="712" spans="1:1">
-      <c r="A712" s="8" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="716" spans="1:1" ht="15">
-      <c r="A716" s="7" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="717" spans="1:1">
-      <c r="A717" s="9"/>
-    </row>
-    <row r="718" spans="1:1" ht="15">
-      <c r="A718" s="7" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="719" spans="1:1" ht="15">
-      <c r="A719" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="720" spans="1:1" ht="15">
-      <c r="A720" s="7" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="721" spans="1:1" ht="15">
-      <c r="A721" s="7" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="722" spans="1:1" ht="15">
-      <c r="A722" s="7" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="723" spans="1:1" ht="15">
-      <c r="A723" s="7" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="724" spans="1:1" ht="15">
-      <c r="A724" s="7" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="728" spans="1:1" ht="15">
-      <c r="A728" s="11" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="729" spans="1:1">
-      <c r="A729" s="9"/>
-    </row>
-    <row r="730" spans="1:1">
-      <c r="A730" s="9" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="731" spans="1:1">
-      <c r="A731" s="9" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="732" spans="1:1">
-      <c r="A732" s="9" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="733" spans="1:1">
-      <c r="A733" s="9" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="734" spans="1:1">
-      <c r="A734" s="9" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="735" spans="1:1">
-      <c r="A735" s="9" t="s">
-        <v>494</v>
+    <row r="29" spans="21:63">
+      <c r="AQ29" s="24" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="30" spans="21:63" ht="15">
+      <c r="BK30" s="28" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="31" spans="21:63">
+      <c r="BK31" s="24" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="32" spans="21:63">
+      <c r="BK32" s="24" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="33" spans="63:63">
+      <c r="BK33" s="24" t="s">
+        <v>550</v>
       </c>
     </row>
   </sheetData>

--- a/Cplusplus/02. C++ FOUNDATIONS.xlsx
+++ b/Cplusplus/02. C++ FOUNDATIONS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="CheckList C++" sheetId="1" r:id="rId1"/>
@@ -1964,6 +1964,8 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
       <t>: Tránh trộn signed và unsigned trong phép so sánh!</t>
@@ -1978,6 +1980,8 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Dùng const/constexpr thay vì #define khi có thể!</t>
@@ -2004,6 +2008,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Tránh C-strings, dùng std::string!</t>
@@ -2019,6 +2025,8 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
       <t>hàm vô danh (anonymous function)</t>
@@ -2028,6 +2036,8 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2148,6 +2158,8 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
       <t>type(parameter</t>
@@ -2157,6 +2169,8 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
       <t>types)&gt; func;</t>
@@ -2220,12 +2234,16 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2233,12 +2251,16 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2246,6 +2268,8 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -4405,7 +4429,7 @@
       <c r="BI122" s="27"/>
     </row>
     <row r="123" spans="1:61" ht="15" x14ac:dyDescent="0.2">
-      <c r="A123" s="27" t="s">
+      <c r="A123" s="9" t="s">
         <v>244</v>
       </c>
       <c r="V123" s="27" t="s">
@@ -4425,8 +4449,8 @@
         <v>337</v>
       </c>
     </row>
-    <row r="124" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A124" s="27" t="s">
+    <row r="124" spans="1:61" ht="15" x14ac:dyDescent="0.2">
+      <c r="A124" s="9" t="s">
         <v>245</v>
       </c>
       <c r="V124" s="27" t="s">
@@ -4439,8 +4463,8 @@
         <v>408</v>
       </c>
     </row>
-    <row r="125" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A125" s="27" t="s">
+    <row r="125" spans="1:61" ht="15" x14ac:dyDescent="0.2">
+      <c r="A125" s="9" t="s">
         <v>246</v>
       </c>
       <c r="V125" s="27" t="s">
